--- a/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-organization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T07:10:15+00:00</t>
+    <t>2026-01-28T12:36:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -718,7 +718,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
